--- a/LoanOfficer-A/2026/184 bidyabati 2.xlsx
+++ b/LoanOfficer-A/2026/184 bidyabati 2.xlsx
@@ -829,7 +829,7 @@
       </c>
       <c r="K1" s="15">
         <f>120-K2</f>
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="L1" s="13"/>
       <c r="M1" s="11"/>
@@ -838,7 +838,7 @@
       </c>
       <c r="O1" s="12">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="P1" s="16"/>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="K2" s="15">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L2" s="13"/>
       <c r="M2" s="11"/>
@@ -876,7 +876,7 @@
       </c>
       <c r="O2" s="18">
         <f>C2-O1</f>
-        <v>11900</v>
+        <v>11300</v>
       </c>
       <c r="P2" s="16"/>
     </row>
@@ -916,9 +916,15 @@
       <c r="A4" s="20">
         <v>2</v>
       </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="20"/>
+      <c r="B4" s="21">
+        <v>46178</v>
+      </c>
+      <c r="C4" s="22">
+        <v>100</v>
+      </c>
+      <c r="D4" s="20">
+        <v>1</v>
+      </c>
       <c r="E4" s="20">
         <v>32</v>
       </c>
@@ -942,9 +948,15 @@
       <c r="A5" s="20">
         <v>3</v>
       </c>
-      <c r="B5" s="21"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="20"/>
+      <c r="B5" s="21">
+        <v>46179</v>
+      </c>
+      <c r="C5" s="22">
+        <v>100</v>
+      </c>
+      <c r="D5" s="20">
+        <v>1</v>
+      </c>
       <c r="E5" s="20">
         <v>33</v>
       </c>
@@ -968,9 +980,15 @@
       <c r="A6" s="20">
         <v>4</v>
       </c>
-      <c r="B6" s="21"/>
-      <c r="C6" s="22"/>
-      <c r="D6" s="20"/>
+      <c r="B6" s="21">
+        <v>46180</v>
+      </c>
+      <c r="C6" s="22">
+        <v>100</v>
+      </c>
+      <c r="D6" s="20">
+        <v>1</v>
+      </c>
       <c r="E6" s="20">
         <v>34</v>
       </c>
@@ -994,9 +1012,15 @@
       <c r="A7" s="20">
         <v>5</v>
       </c>
-      <c r="B7" s="21"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="20"/>
+      <c r="B7" s="21">
+        <v>46181</v>
+      </c>
+      <c r="C7" s="22">
+        <v>100</v>
+      </c>
+      <c r="D7" s="20">
+        <v>1</v>
+      </c>
       <c r="E7" s="20">
         <v>35</v>
       </c>
@@ -1020,9 +1044,15 @@
       <c r="A8" s="20">
         <v>6</v>
       </c>
-      <c r="B8" s="21"/>
-      <c r="C8" s="22"/>
-      <c r="D8" s="20"/>
+      <c r="B8" s="21">
+        <v>46182</v>
+      </c>
+      <c r="C8" s="22">
+        <v>100</v>
+      </c>
+      <c r="D8" s="20">
+        <v>1</v>
+      </c>
       <c r="E8" s="20">
         <v>36</v>
       </c>
@@ -1046,9 +1076,15 @@
       <c r="A9" s="20">
         <v>7</v>
       </c>
-      <c r="B9" s="21"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="20"/>
+      <c r="B9" s="21">
+        <v>46183</v>
+      </c>
+      <c r="C9" s="22">
+        <v>100</v>
+      </c>
+      <c r="D9" s="20">
+        <v>1</v>
+      </c>
       <c r="E9" s="20">
         <v>37</v>
       </c>
